--- a/data/trans_dic/P79$recibos_2023-Habitat-trans_dic.xlsx
+++ b/data/trans_dic/P79$recibos_2023-Habitat-trans_dic.xlsx
@@ -549,17 +549,17 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>5,96%</t>
+          <t>6,85%</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>7,21%</t>
+          <t>7,97%</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>6,63%</t>
+          <t>7,43%</t>
         </is>
       </c>
     </row>
@@ -572,17 +572,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>4,13; 7,94</t>
+          <t>5,18; 9,17</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>5,24; 9,06</t>
+          <t>6,36; 9,8</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>5,45; 8,06</t>
+          <t>6,15; 8,86</t>
         </is>
       </c>
     </row>
@@ -599,17 +599,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>7,19%</t>
+          <t>9,28%</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>9,47%</t>
+          <t>9,75%</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>8,19%</t>
+          <t>9,52%</t>
         </is>
       </c>
     </row>
@@ -622,17 +622,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>3,66; 9,84</t>
+          <t>7,38; 11,46</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>7,97; 11,27</t>
+          <t>8,01; 11,71</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>5,32; 9,8</t>
+          <t>8,23; 10,87</t>
         </is>
       </c>
     </row>
@@ -649,17 +649,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>6,26%</t>
+          <t>6,28%</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>4,99%</t>
+          <t>6,88%</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>5,54%</t>
+          <t>6,58%</t>
         </is>
       </c>
     </row>
@@ -672,17 +672,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>4,72; 8,4</t>
+          <t>4,73; 8,34</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>2,36; 7,2</t>
+          <t>5,28; 8,98</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>3,46; 7,16</t>
+          <t>5,43; 8,03</t>
         </is>
       </c>
     </row>
@@ -699,17 +699,17 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>9,67%</t>
+          <t>10,91%</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>12,71%</t>
+          <t>13,25%</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>11,26%</t>
+          <t>12,15%</t>
         </is>
       </c>
     </row>
@@ -722,17 +722,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>7,74; 11,85</t>
+          <t>8,97; 13,26</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>10,69; 14,71</t>
+          <t>11,37; 15,31</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>10,03; 12,74</t>
+          <t>10,82; 13,72</t>
         </is>
       </c>
     </row>
@@ -749,17 +749,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>7,44%</t>
+          <t>8,59%</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>8,78%</t>
+          <t>9,83%</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>8,12%</t>
+          <t>9,22%</t>
         </is>
       </c>
     </row>
@@ -772,17 +772,17 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>5,82; 8,6</t>
+          <t>7,65; 9,68</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>7,17; 9,77</t>
+          <t>8,95; 10,72</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>6,99; 8,98</t>
+          <t>8,54; 9,94</t>
         </is>
       </c>
     </row>
@@ -907,17 +907,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>36821</t>
+          <t>45918</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>50881</t>
+          <t>56795</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>87702</t>
+          <t>102713</t>
         </is>
       </c>
     </row>
@@ -930,17 +930,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>25535; 49037</t>
+          <t>34717; 61474</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>37017; 63997</t>
+          <t>45298; 69849</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>72094; 106634</t>
+          <t>85078; 122528</t>
         </is>
       </c>
     </row>
@@ -980,17 +980,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>84251</t>
+          <t>94661</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>87324</t>
+          <t>100648</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>171575</t>
+          <t>195308</t>
         </is>
       </c>
     </row>
@@ -1003,17 +1003,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>42880; 115301</t>
+          <t>75361; 116993</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>73528; 103956</t>
+          <t>82626; 120872</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>111438; 205115</t>
+          <t>168849; 223024</t>
         </is>
       </c>
     </row>
@@ -1053,17 +1053,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>42388</t>
+          <t>48248</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>45124</t>
+          <t>53408</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>87512</t>
+          <t>101656</t>
         </is>
       </c>
     </row>
@@ -1076,17 +1076,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>31944; 56841</t>
+          <t>36339; 64135</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>21367; 65058</t>
+          <t>40943; 69666</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>54759; 113258</t>
+          <t>83832; 124096</t>
         </is>
       </c>
     </row>
@@ -1126,17 +1126,17 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>86821</t>
+          <t>104863</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>125716</t>
+          <t>142902</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>212537</t>
+          <t>247765</t>
         </is>
       </c>
     </row>
@@ -1149,17 +1149,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>69463; 106380</t>
+          <t>86146; 127398</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>105756; 145501</t>
+          <t>122642; 165102</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>189298; 240436</t>
+          <t>220704; 279796</t>
         </is>
       </c>
     </row>
@@ -1199,17 +1199,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>250281</t>
+          <t>293689</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>309045</t>
+          <t>353753</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>559326</t>
+          <t>647442</t>
         </is>
       </c>
     </row>
@@ -1222,17 +1222,17 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>195743; 289261</t>
+          <t>261531; 331263</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>252569; 344051</t>
+          <t>322238; 385949</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>481189; 618283</t>
+          <t>599265; 697938</t>
         </is>
       </c>
     </row>
